--- a/projects/project-3/assignment/src/data/to-class-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/to-class-axioms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb5</t>
+          <t>Duration of a temporal extent expressed as a number scaled by a temporal unit</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -480,1197 +480,1208 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb6</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>Alternativa a 'descripción de tiempo' para proporcionar descripción soporte a una duración temporal diferente a utilizar un sistema de calendario/reloj.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb2</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb3</t>
+          <t>Duración de una extensión temporal expresada como un número escalado por una unidad temporal.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb4</t>
+          <t>Time duration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb1</t>
+          <t>n8af765655db349cd8d357fb5dec18556b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Date-time interval</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>Alternative to time:DurationDescription to support description of a temporal duration other than using a calendar/clock system.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Day of week</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Thing</t>
+          <t>n8af765655db349cd8d357fb5dec18556b5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb7</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb13</t>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of year, month, day properties restricted to corresponding XML Schema types xsd:gYear, xsd:gMonth and xsd:gDay, respectively.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb11</t>
+          <t>descripción de fecha-tiempo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb8</t>
+          <t>n8af765655db349cd8d357fb5dec18556b3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb9</t>
+          <t>n8af765655db349cd8d357fb5dec18556b2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb10</t>
+          <t>Date-Time description</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb12</t>
+          <t>n8af765655db349cd8d357fb5dec18556b1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb14</t>
+          <t>Descripción de fecha y tiempo estructurada con valores separados para los diferentes elementos de un sistema calendario-reloj. El sistema de referencia temporal está fijado al calendario gregoriano, y el rango de las propiedades año, mes, día restringidas a los correspondientes tipos del XML Schema xsd:gYear, xsd:gMonth y xsd:gDay respectivamente.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb15</t>
+          <t>n8af765655db349cd8d357fb5dec18556b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb24</t>
+          <t>Date-time interval</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb17</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb25</t>
+          <t>:DateTimeInterval can only be used for an interval whose limits coincide with a date-time element aligned to the calendar and timezone indicated. For example, while both have a duration of one day, the 24-hour interval beginning at midnight at the beginning of 8 May in Central Europe can be expressed as a :DateTimeInterval, but the 24-hour interval starting at 1:30pm cannot.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb19</t>
+          <t>intervalo de fecha-hora</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb18</t>
+          <t>'intervalo de fecha-hora' es una subclase de 'intervalo propio', definida utilizando el multi-elemento 'descripción de fecha-hora'.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb23</t>
+          <t>'intervalo de fecha-hora' se puede utilizar sólo para un intervalo cuyos límites coinciden con un elemento de fecha-hora alineados con el calendario y la zona horaria indicados. Por ejemplo, aunque ambos tienen una duración de un día, el intervalo de 24 horas que empieza en la media noche del comienzo del 8 mayo en Europa Central se puede expresar como un 'intervalo de fecha-hora', el intervalo de 24 horas que empieza a las 1:30pm no.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb26</t>
+          <t>DateTimeInterval is a subclass of ProperInterval, defined using the multi-element DateTimeDescription.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb20</t>
+          <t>El día de la semana</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb16</t>
+          <t>día de la semana</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb21</t>
+          <t>Membership of the class :DayOfWeek is open, to allow for alternative week lengths and different day names.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb22</t>
+          <t>Day of week</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb31</t>
+          <t>The day of week</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb29</t>
+          <t>La pertenencia a la clase 'día de la semana' está abierta, para permitir longitudes de semana alternativas y diferentes nombres de días.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb32</t>
+          <t>Remove enumeration from definition, in order to allow other days to be used when required in other calendars. 
+NOTE: existing days are still present as members of the class, but the class membership is now open. 
+In the original OWL-Time the following constraint appeared: 
+  owl:oneOf (
+      time:Monday
+      time:Tuesday
+      time:Wednesday
+      time:Thursday
+      time:Friday
+      time:Saturday
+      time:Sunday
+    ) ;</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb34</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb33</t>
+          <t>http://www.w3.org/2002/07/owl#Thing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb28</t>
+          <t>En el calendario gregoriano la longitud de los meses no es fija. Por lo tanto, un valor como "2,5 meses" no se puede comparar exactamente con una duración similar expresada en términos de semanas o días.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>n8af765655db349cd8d357fb5dec18556b14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb30</t>
+          <t>n8af765655db349cd8d357fb5dec18556b7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb27</t>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of each of the numeric properties is restricted to xsd:decimal</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb40</t>
+          <t>Duration description</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb37</t>
+          <t>n8af765655db349cd8d357fb5dec18556b12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb38</t>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario. El sistema de referencia temporal se fija al calendario gregoriano, y el intervalo de cada una de las propiedades numéricas se restringe a xsd:decimal.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb42</t>
+          <t>n8af765655db349cd8d357fb5dec18556b9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb41</t>
+          <t>n8af765655db349cd8d357fb5dec18556b11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb44</t>
+          <t>descripción de duración</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb43</t>
+          <t>n8af765655db349cd8d357fb5dec18556b10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb39</t>
+          <t>n8af765655db349cd8d357fb5dec18556b8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Proper interval</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Proper interval</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>n8af765655db349cd8d357fb5dec18556b13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Temporal entity</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Thing</t>
+          <t>In the Gregorian calendar the length of the month is not fixed. Therefore, a value like "2.5 months" cannot be exactly compared with a similar duration expressed in terms of weeks or days.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Temporal position</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb47</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Temporal unit</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Duration</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Time duration</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb5</t>
+          <t>n8af765655db349cd8d357fb5dec18556b22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Duration</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Time duration</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Duration</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Time duration</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb6</t>
+          <t>Algunas combinaciones de propiedades son redundantes - por ejemplo, dentro de un 'año' especificado si se proporciona 'día del año' entonces 'día' y 'mes' se pueden computar, y viceversa. Los valores individuales deberían ser consistentes entre ellos y con el calendario, indicado a través del valor de la propiedad 'tiene TRS'.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Time instant</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>n8af765655db349cd8d357fb5dec18556b15</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Time interval</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>descripción de fecha-hora generalizada</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Time position</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb48</t>
+          <t>Some combinations of properties are redundant - for example, within a specified :year if :dayOfYear is provided then :day and :month can be computed, and vice versa. Individual values should be consistent with each other and the calendar, indicated through the value of the :hasTRS property.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Time position</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>n8af765655db349cd8d357fb5dec18556b21</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb7</t>
+          <t>n8af765655db349cd8d357fb5dec18556b20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb13</t>
+          <t>n8af765655db349cd8d357fb5dec18556b24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>n8af765655db349cd8d357fb5dec18556b25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb11</t>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb8</t>
+          <t>n8af765655db349cd8d357fb5dec18556b16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb9</t>
+          <t>n8af765655db349cd8d357fb5dec18556b19</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb10</t>
+          <t>n8af765655db349cd8d357fb5dec18556b26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb12</t>
+          <t>Descripción de fecha y hora estructurada con valores separados para los distintos elementos de un sistema calendario-reloj.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb14</t>
+          <t>n8af765655db349cd8d357fb5dec18556b17</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb31</t>
+          <t>n8af765655db349cd8d357fb5dec18556b23</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb29</t>
+          <t>n8af765655db349cd8d357fb5dec18556b18</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1693,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb32</t>
+          <t>La extensión de una duración de tiempo expresada como una 'descripción de duración general' depende del Sistema de Referencia Temporal. En algunos calendarios la longitud de la semana o del mes no es constante a lo largo del año. Por tanto, un valor como "25 meses" puede no ser necesariamente ser comparado con un duración similar expresada en términos de semanas o días. Cuando se consideran calendarios que no están basados en el movimiento de la Tierra, se deben tomar incluso más precauciones en la comparación de duraciones.</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1710,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb34</t>
+          <t>n8af765655db349cd8d357fb5dec18556b31</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1727,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb33</t>
+          <t>n8af765655db349cd8d357fb5dec18556b33</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1744,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb28</t>
+          <t>n8af765655db349cd8d357fb5dec18556b27</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1761,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system.</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1778,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb30</t>
+          <t>n8af765655db349cd8d357fb5dec18556b28</t>
         </is>
       </c>
     </row>
@@ -1784,437 +1795,437 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb27</t>
+          <t>n8af765655db349cd8d357fb5dec18556b29</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb15</t>
+          <t>descripción de duración generalizada</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>n8af765655db349cd8d357fb5dec18556b34</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb24</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb17</t>
+          <t>The extent of a time duration expressed as a GeneralDurationDescription depends on the Temporal Reference System. In some calendars the length of the week or month is not constant within the year. Therefore, a value like "2.5 months" may not necessarily be exactly compared with a similar duration expressed in terms of weeks or days. When non-earth-based calendars are considered even more care must be taken in comparing durations.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb25</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb19</t>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb18</t>
+          <t>n8af765655db349cd8d357fb5dec18556b32</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb23</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb26</t>
+          <t>n8af765655db349cd8d357fb5dec18556b30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb20</t>
+          <t xml:space="preserve">Feature at risk - added in 2017 revision, and not yet widely used. </t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb16</t>
+          <t>Membership of the class :MonthOfYear is open, to allow for alternative annual calendars and different month names.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb21</t>
+          <t>n8af765655db349cd8d357fb5dec18556b42</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb22</t>
+          <t>n8af765655db349cd8d357fb5dec18556b37</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>n8af765655db349cd8d357fb5dec18556b39</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb2</t>
+          <t>Month of year</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb3</t>
+          <t>n8af765655db349cd8d357fb5dec18556b40</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb4</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb1</t>
+          <t>n8af765655db349cd8d357fb5dec18556b44</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>día de la semana</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Thing</t>
+          <t>n8af765655db349cd8d357fb5dec18556b43</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>entidad temporal</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Thing</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>instante de tiempo.</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>mes del año</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>intervalo de fecha-hora</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>The month of the year</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>intervalo de tiempo</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>La pertenencia a la clase 'mes del año' está abierta, a permitir calendarios anuales alternativos y diferentes nombres de meses.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>El mes del año.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>Característica en riesgo - añadida en la revisión de 2017, y no utilizada todavía de forma amplia.</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2237,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb40</t>
+          <t>n8af765655db349cd8d357fb5dec18556b38</t>
         </is>
       </c>
     </row>
@@ -2243,199 +2254,4344 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>n8af765655db349cd8d357fb5dec18556b41</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Proper interval</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb37</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Proper interval</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb38</t>
+          <t>Una entidad temporal con extensión o duración distinta de cero, es decir, para la cual los valores de principio y fin del intervalo son diferentes.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Proper interval</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb42</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Proper interval</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb41</t>
+          <t>Proper interval</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Proper interval</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb44</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Proper interval</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb43</t>
+          <t>intervalo propio</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>Proper interval</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb39</t>
+          <t>A temporal entity with non-zero extent or duration, i.e., for which the value of the beginning and end are different</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t>Temporal Reference System</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb48</t>
+          <t>Un sistema de referencia temporal, tal como un sistema de coordenadas temporales (con un origen, una dirección y una escala), una combinación calendario-reloj, o un sistema ordinal (posiblemente jerárquico).
+    Esta clase comodín representa el conjunto de todos los sistemas de referencia temporal.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t>Temporal Reference System</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>posición temporal</t>
+          <t>Temporal Reference System</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>n44f8437f1d0b496b8a43d86637bb788cb47</t>
+          <t>Temporal Reference System</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Temporal Reference System</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Temporal Reference System</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>En el ISO 19108:2002 [ISO19108] se proporciona una taxonomía de sistemas de referencia temporal, incluyendo (a) sistemas de calendario + reloj; (b) sistemas de coordenadas temporales (es decir, desplazamiento numérico a partir de una época); (c) sistemas de referencia ordinales temporales (es decir, secuencia ordenada de intervalos nombrados, no necesariamente de igual duración).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Temporal Reference System</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>A taxonomy of temporal reference systems is provided in ISO 19108:2002 [ISO19108], including (a) calendar + clock systems; (b) temporal coordinate systems (i.e., numeric offset from an epoch); (c) temporal ordinal reference systems (i.e., ordered sequence of named intervals, not necessarily of equal duration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Temporal Reference System</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>A temporal reference system, such as a temporal coordinate system (with an origin, direction, and scale), a calendar-clock combination, or a (possibly hierarchical) ordinal system. 
+This is a stub class, representing the set of all temporal reference systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Temporal duration</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Temporal duration</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>duración temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Temporal duration</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Extensión de tiempo; duración de un intervalo de tiempo independiente de su posición de inicio particular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Temporal duration</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Temporal duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Temporal duration</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Time extent; duration of a time interval separate from its particular start position</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Thing</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Un intervalo temporal o un instante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>A temporal interval or instant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Una posición sobre una línea de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b47</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>A position on a time-line</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>A standard duration, which provides a scale factor for a time extent, or the granularity or precision for a time position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Una duración estándar, que proporciona un factor de escala para una extensión de tiempo, o la granularidad o precisión para una posición de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Remove enumeration from definition, in order to allow other units to be used when required in other coordinate systems. 
+NOTE: existing units are still present as members of the class, but the class membership is now open. 
+In the original OWL-Time the following constraint appeared: 
+  owl:oneOf (
+      time:unitSecond
+      time:unitMinute
+      time:unitHour
+      time:unitDay
+      time:unitWeek
+      time:unitMonth
+      time:unitYear
+    ) ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>La pertenencia de la clase 'unidad de tiempo' está abierta, para permitir otras unidades de tiempo utilizadas en algunas aplicaciones técnicas (por ejemplo, millones de años o el mes Baha'i).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Membership of the class TemporalUnit is open, to allow for other temporal units used in some technical applications (e.g., millions of years, Baha'i month).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Un huso horario designado está asociado con una región geográfica. Sin embargo, para una región particular el desplazamiento desde UTC a menudo varía según las estaciones, y las fechas de los cambios pueden variar de un año a otro. La designación de huso horario  normalmente cambia de una estación a otra (por ejemplo, el horario estándar frente al horario de verano ambos del este de Australia). Además, del desplazamiento para un huso horario puede cambiar sobre escalas de tiempo mayores, aunque su designación no lo haga.
+    Se puede encontrar una guía detallada sobre el funcionamiento de husos horarios en http://www.w3.org/TR/timezone/."@es , "En [owl-time-20060927] se describió una ontología para descripciones de husos horarios, y se proporcionó en un espacio de nombres separado tzont:. Sin embargo, dicha ontología estaba incompleta en su alcance, y el ejemplo de conjuntos de datos (datasets) era selectivo. Además, puesto que el uso de una clase de una ontología externa como el rango de una propiedad de objeto en OWL-Time crea una dependencia, la referencia a la clase huso horario se ha reemplazado por una clase que viene a ser un "cajón de sastre" en la en la parte normativa de esta versión de OWL-Time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>In this implementation TimeZone has no properties defined. It should be thought of as an 'abstract' superclass of all specific timezone implementations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>A designated timezone is associated with a geographic region. However, for a particular region the offset from UTC often varies seasonally, and the dates of the changes may vary from year to year. The timezone designation usually changes for the different seasons (e.g., Australian Eastern Standard Time vs. Australian Eastern Daylight Time). Furthermore, the offset for a timezone may change over longer timescales, though its designation might not.  
+Detailed guidance about working with time zones is given in http://www.w3.org/TR/timezone/ .</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>En la versión original de OWL-Time de 2006, se definió, en un espacio de nombres diferente "http://www.w3.org/2006/timezone#", la clase 'huso horario', con varias propiedades específicas correspondientes a un modelo específico de huso horario.
+    En la versión actual hay una clase con el mismo nombre local en el espacio de nombres de OWL-Time, eliminando la dependencia del espacio de nombres externo.
+    Un axioma de alineación permite que los datos codificados de acuerdo con la versión anterior sean consistentes con la ontología actualizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>En esta implementación 'huso horario' no tiene definidas propiedades. Se debería pensar como una superclase "abstracta" de todas las implementaciones de huso horario específicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  A Time Zone specifies the amount by which the local time is offset from UTC. 
+	A time zone is usually denoted geographically (e.g., Australian Eastern Daylight Time), with a constant value in a given region. 
+The region where it applies and the offset from UTC are specified by a locally recognised governing authority.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In the original 2006 version of OWL-Time, the TimeZone class, with several properties corresponding to a specific model of time-zones, was defined in a separate namespace "http://www.w3.org/2006/timezone#". 
+In the current version a class with same local name is put into the main OWL-Time namespace, removing the dependency on the external namespace. 
+An alignment axiom 
+	tzont:TimeZone rdfs:subClassOf time:TimeZone . 
+allows data encoded according to the previous version to be consistent with the updated ontology. </t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Un huso horario especifica la cantidad en que la hora local está desplazada con respecto a UTC.
+    Un huso horario normalmente se denota geográficamente (p.ej. el horario de verano del este de Australia), con un valor constante en una región dada.
+    La región donde aplica y el desplazamiento desde UTC las especifica una autoridad gubernamental localmente reconocida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>An ontology for time zone descriptions was described in [owl-time-20060927] and provided as RDF in a separate namespace tzont:. However, that ontology was incomplete in scope, and the example datasets were selective. Furthermore, since the use of a class from an external ontology as the range of an ObjectProperty in OWL-Time creates a dependency, reference to the time zone class has been replaced with the 'stub' class in the normative part of this version of OWL-Time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Duration of a temporal extent expressed as a number scaled by a temporal unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Alternativa a 'descripción de tiempo' para proporcionar descripción soporte a una duración temporal diferente a utilizar un sistema de calendario/reloj.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>duración de tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Duración de una extensión temporal expresada como un número escalado por una unidad temporal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Alternative to time:DurationDescription to support description of a temporal duration other than using a calendar/clock system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Time duration</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Una entidad temporal con una extensión o duración cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>A temporal entity with zero extent or duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>A temporal entity with an extent or duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Una entidad temporal con una extensión o duración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Una posición temporal descrita utilizando bien un valor (nominal) de un sistema de referencia ordinal, o un valor (numérico) en un sistema de coordenadas temporales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b48</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A temporal position described using either a (nominal) value from an ordinal reference system, or a (numeric) value in a temporal coordinate system. </t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>En el calendario gregoriano la longitud de los meses no es fija. Por lo tanto, un valor como "2,5 meses" no se puede comparar exactamente con una duración similar expresada en términos de semanas o días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b14</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of each of the numeric properties is restricted to xsd:decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Duration description</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario. El sistema de referencia temporal se fija al calendario gregoriano, y el intervalo de cada una de las propiedades numéricas se restringe a xsd:decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b11</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b13</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>descripción de duración</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>In the Gregorian calendar the length of the month is not fixed. Therefore, a value like "2.5 months" cannot be exactly compared with a similar duration expressed in terms of weeks or days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>La extensión de una duración de tiempo expresada como una 'descripción de duración general' depende del Sistema de Referencia Temporal. En algunos calendarios la longitud de la semana o del mes no es constante a lo largo del año. Por tanto, un valor como "25 meses" puede no ser necesariamente ser comparado con un duración similar expresada en términos de semanas o días. Cuando se consideran calendarios que no están basados en el movimiento de la Tierra, se deben tomar incluso más precauciones en la comparación de duraciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b31</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b33</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b28</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b29</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b34</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>The extent of a time duration expressed as a GeneralDurationDescription depends on the Temporal Reference System. In some calendars the length of the week or month is not constant within the year. Therefore, a value like "2.5 months" may not necessarily be exactly compared with a similar duration expressed in terms of weeks or days. When non-earth-based calendars are considered even more care must be taken in comparing durations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Generalized duration description</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>descripción de duración generalizada</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b30</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Generalized date-time description</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b22</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Algunas combinaciones de propiedades son redundantes - por ejemplo, dentro de un 'año' especificado si se proporciona 'día del año' entonces 'día' y 'mes' se pueden computar, y viceversa. Los valores individuales deberían ser consistentes entre ellos y con el calendario, indicado a través del valor de la propiedad 'tiene TRS'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b15</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Some combinations of properties are redundant - for example, within a specified :year if :dayOfYear is provided then :day and :month can be computed, and vice versa. Individual values should be consistent with each other and the calendar, indicated through the value of the :hasTRS property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b21</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b20</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b24</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b25</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b16</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b19</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b26</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Descripción de fecha y hora estructurada con valores separados para los distintos elementos de un sistema calendario-reloj.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b17</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b23</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>descripción de fecha-hora generalizada</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b18</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of year, month, day properties restricted to corresponding XML Schema types xsd:gYear, xsd:gMonth and xsd:gDay, respectively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Date-Time description</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Descripción de fecha y tiempo estructurada con valores separados para los diferentes elementos de un sistema calendario-reloj. El sistema de referencia temporal está fijado al calendario gregoriano, y el rango de las propiedades año, mes, día restringidas a los correspondientes tipos del XML Schema xsd:gYear, xsd:gMonth y xsd:gDay respectivamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>descripción de fecha-tiempo</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>duración temporal</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>duración temporal</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>duración temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>duración temporal</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Extensión de tiempo; duración de un intervalo de tiempo independiente de su posición de inicio particular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>duración temporal</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Temporal duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>duración temporal</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Time extent; duration of a time interval separate from its particular start position</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>El día de la semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Membership of the class :DayOfWeek is open, to allow for alternative week lengths and different day names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Day of week</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>The day of week</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>La pertenencia a la clase 'día de la semana' está abierta, para permitir longitudes de semana alternativas y diferentes nombres de días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Remove enumeration from definition, in order to allow other days to be used when required in other calendars. 
+NOTE: existing days are still present as members of the class, but the class membership is now open. 
+In the original OWL-Time the following constraint appeared: 
+  owl:oneOf (
+      time:Monday
+      time:Tuesday
+      time:Wednesday
+      time:Thursday
+      time:Friday
+      time:Saturday
+      time:Sunday
+    ) ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Thing</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Temporal entity</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Thing</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Un intervalo temporal o un instante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>A temporal interval or instant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Un huso horario designado está asociado con una región geográfica. Sin embargo, para una región particular el desplazamiento desde UTC a menudo varía según las estaciones, y las fechas de los cambios pueden variar de un año a otro. La designación de huso horario  normalmente cambia de una estación a otra (por ejemplo, el horario estándar frente al horario de verano ambos del este de Australia). Además, del desplazamiento para un huso horario puede cambiar sobre escalas de tiempo mayores, aunque su designación no lo haga.
+    Se puede encontrar una guía detallada sobre el funcionamiento de husos horarios en http://www.w3.org/TR/timezone/."@es , "En [owl-time-20060927] se describió una ontología para descripciones de husos horarios, y se proporcionó en un espacio de nombres separado tzont:. Sin embargo, dicha ontología estaba incompleta en su alcance, y el ejemplo de conjuntos de datos (datasets) era selectivo. Además, puesto que el uso de una clase de una ontología externa como el rango de una propiedad de objeto en OWL-Time crea una dependencia, la referencia a la clase huso horario se ha reemplazado por una clase que viene a ser un "cajón de sastre" en la en la parte normativa de esta versión de OWL-Time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>In this implementation TimeZone has no properties defined. It should be thought of as an 'abstract' superclass of all specific timezone implementations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>A designated timezone is associated with a geographic region. However, for a particular region the offset from UTC often varies seasonally, and the dates of the changes may vary from year to year. The timezone designation usually changes for the different seasons (e.g., Australian Eastern Standard Time vs. Australian Eastern Daylight Time). Furthermore, the offset for a timezone may change over longer timescales, though its designation might not.  
+Detailed guidance about working with time zones is given in http://www.w3.org/TR/timezone/ .</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>En la versión original de OWL-Time de 2006, se definió, en un espacio de nombres diferente "http://www.w3.org/2006/timezone#", la clase 'huso horario', con varias propiedades específicas correspondientes a un modelo específico de huso horario.
+    En la versión actual hay una clase con el mismo nombre local en el espacio de nombres de OWL-Time, eliminando la dependencia del espacio de nombres externo.
+    Un axioma de alineación permite que los datos codificados de acuerdo con la versión anterior sean consistentes con la ontología actualizada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>En esta implementación 'huso horario' no tiene definidas propiedades. Se debería pensar como una superclase "abstracta" de todas las implementaciones de huso horario específicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+  A Time Zone specifies the amount by which the local time is offset from UTC. 
+	A time zone is usually denoted geographically (e.g., Australian Eastern Daylight Time), with a constant value in a given region. 
+The region where it applies and the offset from UTC are specified by a locally recognised governing authority.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In the original 2006 version of OWL-Time, the TimeZone class, with several properties corresponding to a specific model of time-zones, was defined in a separate namespace "http://www.w3.org/2006/timezone#". 
+In the current version a class with same local name is put into the main OWL-Time namespace, removing the dependency on the external namespace. 
+An alignment axiom 
+	tzont:TimeZone rdfs:subClassOf time:TimeZone . 
+allows data encoded according to the previous version to be consistent with the updated ontology. </t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Un huso horario especifica la cantidad en que la hora local está desplazada con respecto a UTC.
+    Un huso horario normalmente se denota geográficamente (p.ej. el horario de verano del este de Australia), con un valor constante en una región dada.
+    La región donde aplica y el desplazamiento desde UTC las especifica una autoridad gubernamental localmente reconocida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>huso horario</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>An ontology for time zone descriptions was described in [owl-time-20060927] and provided as RDF in a separate namespace tzont:. However, that ontology was incomplete in scope, and the example datasets were selective. Furthermore, since the use of a class from an external ontology as the range of an ObjectProperty in OWL-Time creates a dependency, reference to the time zone class has been replaced with the 'stub' class in the normative part of this version of OWL-Time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Una entidad temporal con una extensión o duración cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Time instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>A temporal entity with zero extent or duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>instante de tiempo.</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Date-time interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>:DateTimeInterval can only be used for an interval whose limits coincide with a date-time element aligned to the calendar and timezone indicated. For example, while both have a duration of one day, the 24-hour interval beginning at midnight at the beginning of 8 May in Central Europe can be expressed as a :DateTimeInterval, but the 24-hour interval starting at 1:30pm cannot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>'intervalo de fecha-hora' es una subclase de 'intervalo propio', definida utilizando el multi-elemento 'descripción de fecha-hora'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>'intervalo de fecha-hora' se puede utilizar sólo para un intervalo cuyos límites coinciden con un elemento de fecha-hora alineados con el calendario y la zona horaria indicados. Por ejemplo, aunque ambos tienen una duración de un día, el intervalo de 24 horas que empieza en la media noche del comienzo del 8 mayo en Europa Central se puede expresar como un 'intervalo de fecha-hora', el intervalo de 24 horas que empieza a las 1:30pm no.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>intervalo de fecha-hora</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>DateTimeInterval is a subclass of ProperInterval, defined using the multi-element DateTimeDescription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>A temporal entity with an extent or duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Una entidad temporal con una extensión o duración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>intervalo de tiempo</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Time interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Una entidad temporal con extensión o duración distinta de cero, es decir, para la cual los valores de principio y fin del intervalo son diferentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Proper interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>intervalo propio</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>A temporal entity with non-zero extent or duration, i.e., for which the value of the beginning and end are different</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Feature at risk - added in 2017 revision, and not yet widely used. </t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Membership of the class :MonthOfYear is open, to allow for alternative annual calendars and different month names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b42</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b37</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b39</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Month of year</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b40</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b44</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b43</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>The month of the year</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>La pertenencia a la clase 'mes del año' está abierta, a permitir calendarios anuales alternativos y diferentes nombres de meses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>El mes del año.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Característica en riesgo - añadida en la revisión de 2017, y no utilizada todavía de forma amplia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b38</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>mes del año</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b41</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Una posición temporal descrita utilizando bien un valor (nominal) de un sistema de referencia ordinal, o un valor (numérico) en un sistema de coordenadas temporales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Time position</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b48</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A temporal position described using either a (nominal) value from an ordinal reference system, or a (numeric) value in a temporal coordinate system. </t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Una posición sobre una línea de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>n8af765655db349cd8d357fb5dec18556b47</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>A position on a time-line</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Un sistema de referencia temporal, tal como un sistema de coordenadas temporales (con un origen, una dirección y una escala), una combinación calendario-reloj, o un sistema ordinal (posiblemente jerárquico).
+    Esta clase comodín representa el conjunto de todos los sistemas de referencia temporal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Temporal Reference System</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>En el ISO 19108:2002 [ISO19108] se proporciona una taxonomía de sistemas de referencia temporal, incluyendo (a) sistemas de calendario + reloj; (b) sistemas de coordenadas temporales (es decir, desplazamiento numérico a partir de una época); (c) sistemas de referencia ordinales temporales (es decir, secuencia ordenada de intervalos nombrados, no necesariamente de igual duración).</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>A taxonomy of temporal reference systems is provided in ISO 19108:2002 [ISO19108], including (a) calendar + clock systems; (b) temporal coordinate systems (i.e., numeric offset from an epoch); (c) temporal ordinal reference systems (i.e., ordered sequence of named intervals, not necessarily of equal duration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>sistema de referencia temporal</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>A temporal reference system, such as a temporal coordinate system (with an origin, direction, and scale), a calendar-clock combination, or a (possibly hierarchical) ordinal system. 
+This is a stub class, representing the set of all temporal reference systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>A standard duration, which provides a scale factor for a time extent, or the granularity or precision for a time position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Una duración estándar, que proporciona un factor de escala para una extensión de tiempo, o la granularidad o precisión para una posición de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Remove enumeration from definition, in order to allow other units to be used when required in other coordinate systems. 
+NOTE: existing units are still present as members of the class, but the class membership is now open. 
+In the original OWL-Time the following constraint appeared: 
+  owl:oneOf (
+      time:unitSecond
+      time:unitMinute
+      time:unitHour
+      time:unitDay
+      time:unitWeek
+      time:unitMonth
+      time:unitYear
+    ) ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>La pertenencia de la clase 'unidad de tiempo' está abierta, para permitir otras unidades de tiempo utilizadas en algunas aplicaciones técnicas (por ejemplo, millones de años o el mes Baha'i).</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>unidad de tiempo</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Membership of the class TemporalUnit is open, to allow for other temporal units used in some technical applications (e.g., millions of years, Baha'i month).</t>
         </is>
       </c>
     </row>

--- a/projects/project-3/assignment/src/data/to-class-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/to-class-axioms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C359"/>
+  <dimension ref="A1:C365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>CCOT-Time structural matching spreadsheet identified multiple CCOT Temporal Intervals (Second, Day, Year, and the Multi-Hour/Minute/Second/Day/Week/Month/Year classes) as overlapping with this class. No further axioms are added here because that would push constraints from the narrower CCOT classes onto this broader Time class.</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alternativa a 'descripción de tiempo' para proporcionar descripción soporte a una duración temporal diferente a utilizar un sistema de calendario/reloj.</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>duración de tiempo</t>
+          <t>Alternativa a 'descripción de tiempo' para proporcionar descripción soporte a una duración temporal diferente a utilizar un sistema de calendario/reloj.</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Duración de una extensión temporal expresada como un número escalado por una unidad temporal.</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Time duration</t>
+          <t>Duración de una extensión temporal expresada como un número escalado por una unidad temporal.</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b6</t>
+          <t>Time duration</t>
         </is>
       </c>
     </row>
@@ -599,24 +599,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b5</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b6</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of year, month, day properties restricted to corresponding XML Schema types xsd:gYear, xsd:gMonth and xsd:gDay, respectively.</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b2</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of year, month, day properties restricted to corresponding XML Schema types xsd:gYear, xsd:gMonth and xsd:gDay, respectively.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b3</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b2</t>
+          <t>descripción de fecha-tiempo</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b4</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b1</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b3</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Descripción de fecha y tiempo estructurada con valores separados para los diferentes elementos de un sistema calendario-reloj. El sistema de referencia temporal está fijado al calendario gregoriano, y el rango de las propiedades año, mes, día restringidas a los correspondientes tipos del XML Schema xsd:gYear, xsd:gMonth y xsd:gDay respectivamente.</t>
+          <t>Date-Time description</t>
         </is>
       </c>
     </row>
@@ -769,24 +769,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b4</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Date-time interval</t>
+          <t>Date-Time description</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Descripción de fecha y tiempo estructurada con valores separados para los diferentes elementos de un sistema calendario-reloj. El sistema de referencia temporal está fijado al calendario gregoriano, y el rango de las propiedades año, mes, día restringidas a los correspondientes tipos del XML Schema xsd:gYear, xsd:gMonth y xsd:gDay respectivamente.</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Date-time interval</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>Date-time interval</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>:DateTimeInterval can only be used for an interval whose limits coincide with a date-time element aligned to the calendar and timezone indicated. For example, while both have a duration of one day, the 24-hour interval beginning at midnight at the beginning of 8 May in Central Europe can be expressed as a :DateTimeInterval, but the 24-hour interval starting at 1:30pm cannot.</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>intervalo de fecha-hora</t>
+          <t>:DateTimeInterval can only be used for an interval whose limits coincide with a date-time element aligned to the calendar and timezone indicated. For example, while both have a duration of one day, the 24-hour interval beginning at midnight at the beginning of 8 May in Central Europe can be expressed as a :DateTimeInterval, but the 24-hour interval starting at 1:30pm cannot.</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'intervalo de fecha-hora' es una subclase de 'intervalo propio', definida utilizando el multi-elemento 'descripción de fecha-hora'.</t>
+          <t>intervalo de fecha-hora</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'intervalo de fecha-hora' se puede utilizar sólo para un intervalo cuyos límites coinciden con un elemento de fecha-hora alineados con el calendario y la zona horaria indicados. Por ejemplo, aunque ambos tienen una duración de un día, el intervalo de 24 horas que empieza en la media noche del comienzo del 8 mayo en Europa Central se puede expresar como un 'intervalo de fecha-hora', el intervalo de 24 horas que empieza a las 1:30pm no.</t>
+          <t>'intervalo de fecha-hora' es una subclase de 'intervalo propio', definida utilizando el multi-elemento 'descripción de fecha-hora'.</t>
         </is>
       </c>
     </row>
@@ -905,24 +905,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DateTimeInterval is a subclass of ProperInterval, defined using the multi-element DateTimeDescription.</t>
+          <t>'intervalo de fecha-hora' se puede utilizar sólo para un intervalo cuyos límites coinciden con un elemento de fecha-hora alineados con el calendario y la zona horaria indicados. Por ejemplo, aunque ambos tienen una duración de un día, el intervalo de 24 horas que empieza en la media noche del comienzo del 8 mayo en Europa Central se puede expresar como un 'intervalo de fecha-hora', el intervalo de 24 horas que empieza a las 1:30pm no.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Day of week</t>
+          <t>Date-time interval</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El día de la semana</t>
+          <t>DateTimeInterval is a subclass of ProperInterval, defined using the multi-element DateTimeDescription.</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>día de la semana</t>
+          <t>El día de la semana</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Membership of the class :DayOfWeek is open, to allow for alternative week lengths and different day names.</t>
+          <t>día de la semana</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Day of week</t>
+          <t>Membership of the class :DayOfWeek is open, to allow for alternative week lengths and different day names.</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>The day of week</t>
+          <t>Day of week</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>La pertenencia a la clase 'día de la semana' está abierta, para permitir longitudes de semana alternativas y diferentes nombres de días.</t>
+          <t>The day of week</t>
         </is>
       </c>
     </row>
@@ -1023,6 +1023,23 @@
         </is>
       </c>
       <c r="C36" t="inlineStr">
+        <is>
+          <t>La pertenencia a la clase 'día de la semana' está abierta, para permitir longitudes de semana alternativas y diferentes nombres de días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Day of week</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Remove enumeration from definition, in order to allow other days to be used when required in other calendars. 
 NOTE: existing days are still present as members of the class, but the class membership is now open. 
@@ -1039,23 +1056,6 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Day of week</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -1069,24 +1069,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Thing</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>En el calendario gregoriano la longitud de los meses no es fija. Por lo tanto, un valor como "2,5 meses" no se puede comparar exactamente con una duración similar expresada en términos de semanas o días.</t>
+          <t>http://www.w3.org/2002/07/owl#Thing</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b14</t>
+          <t>En el calendario gregoriano la longitud de los meses no es fija. Por lo tanto, un valor como "2,5 meses" no se puede comparar exactamente con una duración similar expresada en términos de semanas o días.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b7</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of each of the numeric properties is restricted to xsd:decimal</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b11</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of each of the numeric properties is restricted to xsd:decimal</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>Duration description</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b12</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario. El sistema de referencia temporal se fija al calendario gregoriano, y el intervalo de cada una de las propiedades numéricas se restringe a xsd:decimal.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b9</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b9</t>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario. El sistema de referencia temporal se fija al calendario gregoriano, y el intervalo de cada una de las propiedades numéricas se restringe a xsd:decimal.</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b11</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b10</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b10</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b7</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b8</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b13</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b12</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b13</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b8</t>
         </is>
       </c>
     </row>
@@ -1341,24 +1341,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>In the Gregorian calendar the length of the month is not fixed. Therefore, a value like "2.5 months" cannot be exactly compared with a similar duration expressed in terms of weeks or days.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Duration description</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>In the Gregorian calendar the length of the month is not fixed. Therefore, a value like "2.5 months" cannot be exactly compared with a similar duration expressed in terms of weeks or days.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b23</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b22</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b20</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algunas combinaciones de propiedades son redundantes - por ejemplo, dentro de un 'año' especificado si se proporciona 'día del año' entonces 'día' y 'mes' se pueden computar, y viceversa. Los valores individuales deberían ser consistentes entre ellos y con el calendario, indicado a través del valor de la propiedad 'tiene TRS'.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b15</t>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>Algunas combinaciones de propiedades son redundantes - por ejemplo, dentro de un 'año' especificado si se proporciona 'día del año' entonces 'día' y 'mes' se pueden computar, y viceversa. Los valores individuales deberían ser consistentes entre ellos y con el calendario, indicado a través del valor de la propiedad 'tiene TRS'.</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Some combinations of properties are redundant - for example, within a specified :year if :dayOfYear is provided then :day and :month can be computed, and vice versa. Individual values should be consistent with each other and the calendar, indicated through the value of the :hasTRS property.</t>
+          <t>descripción de fecha-hora generalizada</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b21</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b15</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b20</t>
+          <t>Some combinations of properties are redundant - for example, within a specified :year if :dayOfYear is provided then :day and :month can be computed, and vice versa. Individual values should be consistent with each other and the calendar, indicated through the value of the :hasTRS property.</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b24</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b19</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b25</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b25</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b24</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b16</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b22</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b19</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b26</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b26</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b17</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Descripción de fecha y hora estructurada con valores separados para los distintos elementos de un sistema calendario-reloj.</t>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b17</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b16</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b23</t>
+          <t>Descripción de fecha y hora estructurada con valores separados para los distintos elementos de un sistema calendario-reloj.</t>
         </is>
       </c>
     </row>
@@ -1681,24 +1681,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b18</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b18</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>La extensión de una duración de tiempo expresada como una 'descripción de duración general' depende del Sistema de Referencia Temporal. En algunos calendarios la longitud de la semana o del mes no es constante a lo largo del año. Por tanto, un valor como "25 meses" puede no ser necesariamente ser comparado con un duración similar expresada en términos de semanas o días. Cuando se consideran calendarios que no están basados en el movimiento de la Tierra, se deben tomar incluso más precauciones en la comparación de duraciones.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b21</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b31</t>
+          <t>La extensión de una duración de tiempo expresada como una 'descripción de duración general' depende del Sistema de Referencia Temporal. En algunos calendarios la longitud de la semana o del mes no es constante a lo largo del año. Por tanto, un valor como "25 meses" puede no ser necesariamente ser comparado con un duración similar expresada en términos de semanas o días. Cuando se consideran calendarios que no están basados en el movimiento de la Tierra, se deben tomar incluso más precauciones en la comparación de duraciones.</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b33</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b28</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b27</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b32</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b31</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b28</t>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system.</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b29</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b33</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b34</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b34</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The extent of a time duration expressed as a GeneralDurationDescription depends on the Temporal Reference System. In some calendars the length of the week or month is not constant within the year. Therefore, a value like "2.5 months" may not necessarily be exactly compared with a similar duration expressed in terms of weeks or days. When non-earth-based calendars are considered even more care must be taken in comparing durations.</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>The extent of a time duration expressed as a GeneralDurationDescription depends on the Temporal Reference System. In some calendars the length of the week or month is not constant within the year. Therefore, a value like "2.5 months" may not necessarily be exactly compared with a similar duration expressed in terms of weeks or days. When non-earth-based calendars are considered even more care must be taken in comparing durations.</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b32</t>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario.</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b27</t>
         </is>
       </c>
     </row>
@@ -1953,24 +1953,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b30</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feature at risk - added in 2017 revision, and not yet widely used. </t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b29</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Membership of the class :MonthOfYear is open, to allow for alternative annual calendars and different month names.</t>
+          <t xml:space="preserve">Feature at risk - added in 2017 revision, and not yet widely used. </t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b42</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b40</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b37</t>
+          <t>Membership of the class :MonthOfYear is open, to allow for alternative annual calendars and different month names.</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b39</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b42</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b40</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b39</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b44</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b43</t>
+          <t>mes del año</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>The month of the year</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>La pertenencia a la clase 'mes del año' está abierta, a permitir calendarios anuales alternativos y diferentes nombres de meses.</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>The month of the year</t>
+          <t>El mes del año.</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>La pertenencia a la clase 'mes del año' está abierta, a permitir calendarios anuales alternativos y diferentes nombres de meses.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b37</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>El mes del año.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b44</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Característica en riesgo - añadida en la revisión de 2017, y no utilizada todavía de forma amplia.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b41</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b38</t>
+          <t>Característica en riesgo - añadida en la revisión de 2017, y no utilizada todavía de forma amplia.</t>
         </is>
       </c>
     </row>
@@ -2259,24 +2259,24 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b41</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b43</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Proper interval</t>
+          <t>Month of year</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b38</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Una entidad temporal con extensión o duración distinta de cero, es decir, para la cual los valores de principio y fin del intervalo son diferentes.</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Una entidad temporal con extensión o duración distinta de cero, es decir, para la cual los valores de principio y fin del intervalo son diferentes.</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Proper interval</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>Proper interval</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
     </row>
@@ -2378,45 +2378,45 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>A temporal entity with non-zero extent or duration, i.e., for which the value of the beginning and end are different</t>
+          <t>intervalo propio</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Proper interval</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>A temporal entity with non-zero extent or duration, i.e., for which the value of the beginning and end are different</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Temporal Reference System</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Un sistema de referencia temporal, tal como un sistema de coordenadas temporales (con un origen, una dirección y una escala), una combinación calendario-reloj, o un sistema ordinal (posiblemente jerárquico).
     Esta clase comodín representa el conjunto de todos los sistemas de referencia temporal.</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TRS</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Temporal Reference System</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
-        </is>
-      </c>
-    </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Temporal Reference System</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>sistema de referencia temporal</t>
+          <t>Temporal Reference System</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>En el ISO 19108:2002 [ISO19108] se proporciona una taxonomía de sistemas de referencia temporal, incluyendo (a) sistemas de calendario + reloj; (b) sistemas de coordenadas temporales (es decir, desplazamiento numérico a partir de una época); (c) sistemas de referencia ordinales temporales (es decir, secuencia ordenada de intervalos nombrados, no necesariamente de igual duración).</t>
+          <t>sistema de referencia temporal</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>A taxonomy of temporal reference systems is provided in ISO 19108:2002 [ISO19108], including (a) calendar + clock systems; (b) temporal coordinate systems (i.e., numeric offset from an epoch); (c) temporal ordinal reference systems (i.e., ordered sequence of named intervals, not necessarily of equal duration).</t>
+          <t>En el ISO 19108:2002 [ISO19108] se proporciona una taxonomía de sistemas de referencia temporal, incluyendo (a) sistemas de calendario + reloj; (b) sistemas de coordenadas temporales (es decir, desplazamiento numérico a partir de una época); (c) sistemas de referencia ordinales temporales (es decir, secuencia ordenada de intervalos nombrados, no necesariamente de igual duración).</t>
         </is>
       </c>
     </row>
@@ -2498,28 +2498,28 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>A taxonomy of temporal reference systems is provided in ISO 19108:2002 [ISO19108], including (a) calendar + clock systems; (b) temporal coordinate systems (i.e., numeric offset from an epoch); (c) temporal ordinal reference systems (i.e., ordered sequence of named intervals, not necessarily of equal duration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TRS</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Temporal Reference System</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
           <t>A temporal reference system, such as a temporal coordinate system (with an origin, direction, and scale), a calendar-clock combination, or a (possibly hierarchical) ordinal system. 
 This is a stub class, representing the set of all temporal reference systems.</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Temporal duration</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
-        </is>
-      </c>
-    </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>duración temporal</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Extensión de tiempo; duración de un intervalo de tiempo independiente de su posición de inicio particular.</t>
+          <t>duración temporal</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Temporal duration</t>
+          <t>Extensión de tiempo; duración de un intervalo de tiempo independiente de su posición de inicio particular.</t>
         </is>
       </c>
     </row>
@@ -2584,24 +2584,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Time extent; duration of a time interval separate from its particular start position</t>
+          <t>Temporal duration</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Temporal entity</t>
+          <t>Temporal duration</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Temporal entity</t>
+          <t>Time extent; duration of a time interval separate from its particular start position</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>entidad temporal</t>
+          <t>Temporal entity</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>entidad temporal</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Thing</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b45</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Un intervalo temporal o un instante.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>A temporal interval or instant.</t>
+          <t>http://www.w3.org/2002/07/owl#Thing</t>
         </is>
       </c>
     </row>
@@ -2703,24 +2703,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b45</t>
+          <t>Un intervalo temporal o un instante.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Temporal position</t>
+          <t>Temporal entity</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>A temporal interval or instant.</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Una posición sobre una línea de tiempo.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>posición temporal</t>
+          <t>Una posición sobre una línea de tiempo.</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b47</t>
+          <t>CCOT-Time structural matching spreadsheet identified cco:ont00000223 (Time of Day) as overlapping with this class. No further axioms are added here because that would push constraints from the narrower CCOT class onto this broader Time class.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>A position on a time-line</t>
+          <t>posición temporal</t>
         </is>
       </c>
     </row>
@@ -2805,41 +2805,41 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Temporal position</t>
+          <t>A position on a time-line</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Temporal unit</t>
+          <t>Temporal position</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>unidad de tiempo</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b47</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Temporal unit</t>
+          <t>Temporal position</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>A standard duration, which provides a scale factor for a time extent, or the granularity or precision for a time position.</t>
+          <t>Temporal position</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>unidad de tiempo</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>A standard duration, which provides a scale factor for a time extent, or the granularity or precision for a time position.</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Una duración estándar, que proporciona un factor de escala para una extensión de tiempo, o la granularidad o precisión para una posición de tiempo.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2906,6 +2906,40 @@
         </is>
       </c>
       <c r="C146" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Una duración estándar, que proporciona un factor de escala para una extensión de tiempo, o la granularidad o precisión para una posición de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>Remove enumeration from definition, in order to allow other units to be used when required in other coordinate systems. 
 NOTE: existing units are still present as members of the class, but the class membership is now open. 
@@ -2922,40 +2956,6 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TemporalUnit</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Temporal unit</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>La pertenencia de la clase 'unidad de tiempo' está abierta, para permitir otras unidades de tiempo utilizadas en algunas aplicaciones técnicas (por ejemplo, millones de años o el mes Baha'i).</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TemporalUnit</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Temporal unit</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Temporal unit</t>
-        </is>
-      </c>
-    </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
@@ -2969,75 +2969,109 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Membership of the class TemporalUnit is open, to allow for other temporal units used in some technical applications (e.g., millions of years, Baha'i month).</t>
+          <t>La pertenencia de la clase 'unidad de tiempo' está abierta, para permitir otras unidades de tiempo utilizadas en algunas aplicaciones técnicas (por ejemplo, millones de años o el mes Baha'i).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalUnit</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Temporal unit</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Membership of the class TemporalUnit is open, to allow for other temporal units used in some technical applications (e.g., millions of years, Baha'i month).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Un huso horario designado está asociado con una región geográfica. Sin embargo, para una región particular el desplazamiento desde UTC a menudo varía según las estaciones, y las fechas de los cambios pueden variar de un año a otro. La designación de huso horario  normalmente cambia de una estación a otra (por ejemplo, el horario estándar frente al horario de verano ambos del este de Australia). Además, del desplazamiento para un huso horario puede cambiar sobre escalas de tiempo mayores, aunque su designación no lo haga.
     Se puede encontrar una guía detallada sobre el funcionamiento de husos horarios en http://www.w3.org/TR/timezone/."@es , "En [owl-time-20060927] se describió una ontología para descripciones de husos horarios, y se proporcionó en un espacio de nombres separado tzont:. Sin embargo, dicha ontología estaba incompleta en su alcance, y el ejemplo de conjuntos de datos (datasets) era selectivo. Además, puesto que el uso de una clase de una ontología externa como el rango de una propiedad de objeto en OWL-Time crea una dependencia, la referencia a la clase huso horario se ha reemplazado por una clase que viene a ser un "cajón de sastre" en la en la parte normativa de esta versión de OWL-Time.</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>In this implementation TimeZone has no properties defined. It should be thought of as an 'abstract' superclass of all specific timezone implementations.</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>A designated timezone is associated with a geographic region. However, for a particular region the offset from UTC often varies seasonally, and the dates of the changes may vary from year to year. The timezone designation usually changes for the different seasons (e.g., Australian Eastern Standard Time vs. Australian Eastern Daylight Time). Furthermore, the offset for a timezone may change over longer timescales, though its designation might not.  
 Detailed guidance about working with time zones is given in http://www.w3.org/TR/timezone/ .</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>En la versión original de OWL-Time de 2006, se definió, en un espacio de nombres diferente "http://www.w3.org/2006/timezone#", la clase 'huso horario', con varias propiedades específicas correspondientes a un modelo específico de huso horario.
     En la versión actual hay una clase con el mismo nombre local en el espacio de nombres de OWL-Time, eliminando la dependencia del espacio de nombres externo.
@@ -3045,40 +3079,6 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TimeZone</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Time Zone</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>huso horario</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TimeZone</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Time Zone</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
-        </is>
-      </c>
-    </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>En esta implementación 'huso horario' no tiene definidas propiedades. Se debería pensar como una superclase "abstracta" de todas las implementaciones de huso horario específicas.</t>
+          <t>huso horario</t>
         </is>
       </c>
     </row>
@@ -3108,6 +3108,40 @@
         </is>
       </c>
       <c r="C157" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>En esta implementación 'huso horario' no tiene definidas propiedades. Se debería pensar como una superclase "abstracta" de todas las implementaciones de huso horario específicas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Time Zone</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t xml:space="preserve">
   A Time Zone specifies the amount by which the local time is offset from UTC. 
@@ -3117,18 +3151,18 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t xml:space="preserve">In the original 2006 version of OWL-Time, the TimeZone class, with several properties corresponding to a specific model of time-zones, was defined in a separate namespace "http://www.w3.org/2006/timezone#". 
 In the current version a class with same local name is put into the main OWL-Time namespace, removing the dependency on the external namespace. 
@@ -3138,35 +3172,35 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>Un huso horario especifica la cantidad en que la hora local está desplazada con respecto a UTC.
     Un huso horario normalmente se denota geográficamente (p.ej. el horario de verano del este de Australia), con un valor constante en una región dada.
@@ -3174,54 +3208,20 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TimeZone</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Time Zone</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>An ontology for time zone descriptions was described in [owl-time-20060927] and provided as RDF in a separate namespace tzont:. However, that ontology was incomplete in scope, and the example datasets were selective. Furthermore, since the use of a class from an external ontology as the range of an ObjectProperty in OWL-Time creates a dependency, reference to the time zone class has been replaced with the 'stub' class in the normative part of this version of OWL-Time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#Duration</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Time duration</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Duration of a temporal extent expressed as a number scaled by a temporal unit</t>
-        </is>
-      </c>
-    </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Duration</t>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Time duration</t>
+          <t>Time Zone</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>An ontology for time zone descriptions was described in [owl-time-20060927] and provided as RDF in a separate namespace tzont:. However, that ontology was incomplete in scope, and the example datasets were selective. Furthermore, since the use of a class from an external ontology as the range of an ObjectProperty in OWL-Time creates a dependency, reference to the time zone class has been replaced with the 'stub' class in the normative part of this version of OWL-Time.</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>Duration of a temporal extent expressed as a number scaled by a temporal unit</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Alternativa a 'descripción de tiempo' para proporcionar descripción soporte a una duración temporal diferente a utilizar un sistema de calendario/reloj.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>duración de tiempo</t>
+          <t>CCOT-Time structural matching spreadsheet identified multiple CCOT Temporal Intervals (Second, Day, Year, and the Multi-Hour/Minute/Second/Day/Week/Month/Year classes) as overlapping with this class. No further axioms are added here because that would push constraints from the narrower CCOT classes onto this broader Time class.</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Duración de una extensión temporal expresada como un número escalado por una unidad temporal.</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Time duration</t>
+          <t>Alternativa a 'descripción de tiempo' para proporcionar descripción soporte a una duración temporal diferente a utilizar un sistema de calendario/reloj.</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b6</t>
+          <t>duración de tiempo</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Alternative to time:DurationDescription to support description of a temporal duration other than using a calendar/clock system.</t>
+          <t>Duración de una extensión temporal expresada como un número escalado por una unidad temporal.</t>
         </is>
       </c>
     </row>
@@ -3357,58 +3357,58 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b5</t>
+          <t>Time duration</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Time instant</t>
+          <t>Time duration</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Una entidad temporal con una extensión o duración cero.</t>
+          <t>Alternative to time:DurationDescription to support description of a temporal duration other than using a calendar/clock system.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Time instant</t>
+          <t>Time duration</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Time instant</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Time instant</t>
+          <t>Time duration</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>instante de tiempo.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b6</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Una entidad temporal con una extensión o duración cero.</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>A temporal entity with zero extent or duration</t>
+          <t>Time instant</t>
         </is>
       </c>
     </row>
@@ -3459,58 +3459,58 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>instante de tiempo.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Time interval</t>
+          <t>Time instant</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>intervalo de tiempo</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Time interval</t>
+          <t>Time instant</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>A temporal entity with an extent or duration</t>
+          <t>A temporal entity with zero extent or duration</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Time interval</t>
+          <t>Time instant</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>intervalo de tiempo</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Una entidad temporal con una extensión o duración.</t>
+          <t>A temporal entity with an extent or duration</t>
         </is>
       </c>
     </row>
@@ -3561,58 +3561,58 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Time interval</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Time position</t>
+          <t>Time interval</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Una posición temporal descrita utilizando bien un valor (nominal) de un sistema de referencia ordinal, o un valor (numérico) en un sistema de coordenadas temporales.</t>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Time position</t>
+          <t>Time interval</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Time position</t>
+          <t>Una entidad temporal con una extensión o duración.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Time position</t>
+          <t>Time interval</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b48</t>
+          <t>Time interval</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">A temporal position described using either a (nominal) value from an ordinal reference system, or a (numeric) value in a temporal coordinate system. </t>
+          <t>Una posición temporal descrita utilizando bien un valor (nominal) de un sistema de referencia ordinal, o un valor (numérico) en un sistema de coordenadas temporales.</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Time position</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t xml:space="preserve">A temporal position described using either a (nominal) value from an ordinal reference system, or a (numeric) value in a temporal coordinate system. </t>
         </is>
       </c>
     </row>
@@ -3680,75 +3680,75 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t>CCOT-Time structural matching spreadsheet identified cco:ont00000359 (Julian Date) as overlapping with this class. No further axioms are added here because that would push constraints from the narrower CCOT class onto this broader Time class.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Time position</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>En el calendario gregoriano la longitud de los meses no es fija. Por lo tanto, un valor como "2,5 meses" no se puede comparar exactamente con una duración similar expresada en términos de semanas o días.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Time position</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b14</t>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Time position</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b7</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b48</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DurationDescription</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>Time position</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of each of the numeric properties is restricted to xsd:decimal</t>
+          <t>posición de tiempo</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Duration description</t>
+          <t>En el calendario gregoriano la longitud de los meses no es fija. Por lo tanto, un valor como "2,5 meses" no se puede comparar exactamente con una duración similar expresada en términos de semanas o días.</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b14</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b12</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b11</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario. El sistema de referencia temporal se fija al calendario gregoriano, y el intervalo de cada una de las propiedades numéricas se restringe a xsd:decimal.</t>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of each of the numeric properties is restricted to xsd:decimal</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b9</t>
+          <t>Duration description</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b11</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>descripción de duración</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b9</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b10</t>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario. El sistema de referencia temporal se fija al calendario gregoriano, y el intervalo de cada una de las propiedades numéricas se restringe a xsd:decimal.</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b8</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b10</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>descripción de duración</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b13</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b7</t>
         </is>
       </c>
     </row>
@@ -3952,75 +3952,75 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>In the Gregorian calendar the length of the month is not fixed. Therefore, a value like "2.5 months" cannot be exactly compared with a similar duration expressed in terms of weeks or days.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b13</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>descripción de duración</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>La extensión de una duración de tiempo expresada como una 'descripción de duración general' depende del Sistema de Referencia Temporal. En algunos calendarios la longitud de la semana o del mes no es constante a lo largo del año. Por tanto, un valor como "25 meses" puede no ser necesariamente ser comparado con un duración similar expresada en términos de semanas o días. Cuando se consideran calendarios que no están basados en el movimiento de la Tierra, se deben tomar incluso más precauciones en la comparación de duraciones.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b12</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>descripción de duración</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b31</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b8</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>descripción de duración</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b33</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
+          <t>http://www.w3.org/2006/time#DurationDescription</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>descripción de duración</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b27</t>
+          <t>In the Gregorian calendar the length of the month is not fixed. Therefore, a value like "2.5 months" cannot be exactly compared with a similar duration expressed in terms of weeks or days.</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system.</t>
+          <t>La extensión de una duración de tiempo expresada como una 'descripción de duración general' depende del Sistema de Referencia Temporal. En algunos calendarios la longitud de la semana o del mes no es constante a lo largo del año. Por tanto, un valor como "25 meses" puede no ser necesariamente ser comparado con un duración similar expresada en términos de semanas o días. Cuando se consideran calendarios que no están basados en el movimiento de la Tierra, se deben tomar incluso más precauciones en la comparación de duraciones.</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b28</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b28</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b29</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b32</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>descripción de duración generalizada</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b31</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b34</t>
+          <t>Description of temporal extent structured with separate values for the various elements of a calendar-clock system.</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b33</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>The extent of a time duration expressed as a GeneralDurationDescription depends on the Temporal Reference System. In some calendars the length of the week or month is not constant within the year. Therefore, a value like "2.5 months" may not necessarily be exactly compared with a similar duration expressed in terms of weeks or days. When non-earth-based calendars are considered even more care must be taken in comparing durations.</t>
+          <t>descripción de duración generalizada</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b30</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b34</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b32</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Generalized duration description</t>
+          <t>The extent of a time duration expressed as a GeneralDurationDescription depends on the Temporal Reference System. In some calendars the length of the week or month is not constant within the year. Therefore, a value like "2.5 months" may not necessarily be exactly compared with a similar duration expressed in terms of weeks or days. When non-earth-based calendars are considered even more care must be taken in comparing durations.</t>
         </is>
       </c>
     </row>
@@ -4224,75 +4224,75 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b30</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>descripción de duración generalizada</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Generalized date-time description</t>
+          <t>Descripción de extensión temporal estructurada con valores separados para los distintos elementos de un sistema de horario-calendario.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>descripción de duración generalizada</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b27</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>descripción de duración generalizada</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b22</t>
+          <t>Generalized duration description</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDurationDescription</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>descripción de duración generalizada</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b29</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Algunas combinaciones de propiedades son redundantes - por ejemplo, dentro de un 'año' especificado si se proporciona 'día del año' entonces 'día' y 'mes' se pueden computar, y viceversa. Los valores individuales deberían ser consistentes entre ellos y con el calendario, indicado a través del valor de la propiedad 'tiene TRS'.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b23</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b15</t>
+          <t>Generalized date-time description</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>descripción de fecha-hora generalizada</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b20</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Some combinations of properties are redundant - for example, within a specified :year if :dayOfYear is provided then :day and :month can be computed, and vice versa. Individual values should be consistent with each other and the calendar, indicated through the value of the :hasTRS property.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b21</t>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b20</t>
+          <t>Algunas combinaciones de propiedades son redundantes - por ejemplo, dentro de un 'año' especificado si se proporciona 'día del año' entonces 'día' y 'mes' se pueden computar, y viceversa. Los valores individuales deberían ser consistentes entre ellos y con el calendario, indicado a través del valor de la propiedad 'tiene TRS'.</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b24</t>
+          <t>descripción de fecha-hora generalizada</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b25</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b15</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system</t>
+          <t>Some combinations of properties are redundant - for example, within a specified :year if :dayOfYear is provided then :day and :month can be computed, and vice versa. Individual values should be consistent with each other and the calendar, indicated through the value of the :hasTRS property.</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b16</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b19</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b19</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b25</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b26</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b24</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Descripción de fecha y hora estructurada con valores separados para los distintos elementos de un sistema calendario-reloj.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b22</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b17</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b26</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b23</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b17</t>
         </is>
       </c>
     </row>
@@ -4564,75 +4564,75 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b18</t>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>descripción de fecha-hora generalizada</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b16</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>descripción de fecha-hora generalizada</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of year, month, day properties restricted to corresponding XML Schema types xsd:gYear, xsd:gMonth and xsd:gDay, respectively.</t>
+          <t>Descripción de fecha y hora estructurada con valores separados para los distintos elementos de un sistema calendario-reloj.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>descripción de fecha-hora generalizada</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b18</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>descripción de fecha-hora generalizada</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>descripción de fecha-tiempo</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b21</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b3</t>
+          <t>http://www.w3.org/2006/time#GeneralDateTimeDescription</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b2</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b2</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Date-Time description</t>
+          <t>Description of date and time structured with separate values for the various elements of a calendar-clock system. The temporal reference system is fixed to Gregorian Calendar, and the range of year, month, day properties restricted to corresponding XML Schema types xsd:gYear, xsd:gMonth and xsd:gDay, respectively.</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b1</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Descripción de fecha y tiempo estructurada con valores separados para los diferentes elementos de un sistema calendario-reloj. El sistema de referencia temporal está fijado al calendario gregoriano, y el rango de las propiedades año, mes, día restringidas a los correspondientes tipos del XML Schema xsd:gYear, xsd:gMonth y xsd:gDay respectivamente.</t>
+          <t>descripción de fecha-tiempo</t>
         </is>
       </c>
     </row>
@@ -4734,75 +4734,75 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b4</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b4</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>duración temporal</t>
+          <t>descripción de fecha-tiempo</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b3</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>duración temporal</t>
+          <t>descripción de fecha-tiempo</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>duración temporal</t>
+          <t>Date-Time description</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>duración temporal</t>
+          <t>descripción de fecha-tiempo</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Extensión de tiempo; duración de un intervalo de tiempo independiente de su posición de inicio particular.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b1</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalDuration</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>duración temporal</t>
+          <t>descripción de fecha-tiempo</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Temporal duration</t>
+          <t>Descripción de fecha y tiempo estructurada con valores separados para los diferentes elementos de un sistema calendario-reloj. El sistema de referencia temporal está fijado al calendario gregoriano, y el rango de las propiedades año, mes, día restringidas a los correspondientes tipos del XML Schema xsd:gYear, xsd:gMonth y xsd:gDay respectivamente.</t>
         </is>
       </c>
     </row>
@@ -4819,75 +4819,75 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Time extent; duration of a time interval separate from its particular start position</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>día de la semana</t>
+          <t>duración temporal</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>El día de la semana</t>
+          <t>duración temporal</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>día de la semana</t>
+          <t>duración temporal</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>día de la semana</t>
+          <t>Extensión de tiempo; duración de un intervalo de tiempo independiente de su posición de inicio particular.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>día de la semana</t>
+          <t>duración temporal</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Membership of the class :DayOfWeek is open, to allow for alternative week lengths and different day names.</t>
+          <t>Temporal duration</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+          <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>día de la semana</t>
+          <t>duración temporal</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Day of week</t>
+          <t>Time extent; duration of a time interval separate from its particular start position</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>The day of week</t>
+          <t>El día de la semana</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La pertenencia a la clase 'día de la semana' está abierta, para permitir longitudes de semana alternativas y diferentes nombres de días.</t>
+          <t>día de la semana</t>
         </is>
       </c>
     </row>
@@ -4937,6 +4937,74 @@
         </is>
       </c>
       <c r="C264" t="inlineStr">
+        <is>
+          <t>Membership of the class :DayOfWeek is open, to allow for alternative week lengths and different day names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Day of week</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>The day of week</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>La pertenencia a la clase 'día de la semana' está abierta, para permitir longitudes de semana alternativas y diferentes nombres de días.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>día de la semana</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
         <is>
           <t>Remove enumeration from definition, in order to allow other days to be used when required in other calendars. 
 NOTE: existing days are still present as members of the class, but the class membership is now open. 
@@ -4953,83 +5021,15 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>día de la semana</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#DayOfWeek</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>día de la semana</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2002/07/owl#Thing</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>entidad temporal</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Temporal entity</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>entidad temporal</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>entidad temporal</t>
-        </is>
-      </c>
-    </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>entidad temporal</t>
+          <t>día de la semana</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5041,12 +5041,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>http://www.w3.org/2006/time#DayOfWeek</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>entidad temporal</t>
+          <t>día de la semana</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Un intervalo temporal o un instante.</t>
+          <t>Temporal entity</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>A temporal interval or instant.</t>
+          <t>entidad temporal</t>
         </is>
       </c>
     </row>
@@ -5102,75 +5102,143 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b45</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b45</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Thing</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Un intervalo temporal o un instante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>entidad temporal</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>A temporal interval or instant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>Un huso horario designado está asociado con una región geográfica. Sin embargo, para una región particular el desplazamiento desde UTC a menudo varía según las estaciones, y las fechas de los cambios pueden variar de un año a otro. La designación de huso horario  normalmente cambia de una estación a otra (por ejemplo, el horario estándar frente al horario de verano ambos del este de Australia). Además, del desplazamiento para un huso horario puede cambiar sobre escalas de tiempo mayores, aunque su designación no lo haga.
     Se puede encontrar una guía detallada sobre el funcionamiento de husos horarios en http://www.w3.org/TR/timezone/."@es , "En [owl-time-20060927] se describió una ontología para descripciones de husos horarios, y se proporcionó en un espacio de nombres separado tzont:. Sin embargo, dicha ontología estaba incompleta en su alcance, y el ejemplo de conjuntos de datos (datasets) era selectivo. Además, puesto que el uso de una clase de una ontología externa como el rango de una propiedad de objeto en OWL-Time crea una dependencia, la referencia a la clase huso horario se ha reemplazado por una clase que viene a ser un "cajón de sastre" en la en la parte normativa de esta versión de OWL-Time.</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>In this implementation TimeZone has no properties defined. It should be thought of as an 'abstract' superclass of all specific timezone implementations.</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>A designated timezone is associated with a geographic region. However, for a particular region the offset from UTC often varies seasonally, and the dates of the changes may vary from year to year. The timezone designation usually changes for the different seasons (e.g., Australian Eastern Standard Time vs. Australian Eastern Daylight Time). Furthermore, the offset for a timezone may change over longer timescales, though its designation might not.  
 Detailed guidance about working with time zones is given in http://www.w3.org/TR/timezone/ .</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>En la versión original de OWL-Time de 2006, se definió, en un espacio de nombres diferente "http://www.w3.org/2006/timezone#", la clase 'huso horario', con varias propiedades específicas correspondientes a un modelo específico de huso horario.
     En la versión actual hay una clase con el mismo nombre local en el espacio de nombres de OWL-Time, eliminando la dependencia del espacio de nombres externo.
@@ -5178,69 +5246,69 @@
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>En esta implementación 'huso horario' no tiene definidas propiedades. Se debería pensar como una superclase "abstracta" de todas las implementaciones de huso horario específicas.</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C285" t="inlineStr">
         <is>
           <t xml:space="preserve">
   A Time Zone specifies the amount by which the local time is offset from UTC. 
@@ -5250,18 +5318,18 @@
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="C286" t="inlineStr">
         <is>
           <t xml:space="preserve">In the original 2006 version of OWL-Time, the TimeZone class, with several properties corresponding to a specific model of time-zones, was defined in a separate namespace "http://www.w3.org/2006/timezone#". 
 In the current version a class with same local name is put into the main OWL-Time namespace, removing the dependency on the external namespace. 
@@ -5271,35 +5339,35 @@
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C287" t="inlineStr">
         <is>
           <t>Time Zone</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>huso horario</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C288" t="inlineStr">
         <is>
           <t>Un huso horario especifica la cantidad en que la hora local está desplazada con respecto a UTC.
     Un huso horario normalmente se denota geográficamente (p.ej. el horario de verano del este de Australia), con un valor constante en una región dada.
@@ -5307,88 +5375,20 @@
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#TimeZone</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>huso horario</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>An ontology for time zone descriptions was described in [owl-time-20060927] and provided as RDF in a separate namespace tzont:. However, that ontology was incomplete in scope, and the example datasets were selective. Furthermore, since the use of a class from an external ontology as the range of an ObjectProperty in OWL-Time creates a dependency, reference to the time zone class has been replaced with the 'stub' class in the normative part of this version of OWL-Time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>instante de tiempo.</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Una entidad temporal con una extensión o duración cero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>instante de tiempo.</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Time instant</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>instante de tiempo.</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>instante de tiempo.</t>
-        </is>
-      </c>
-    </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2006/time#TimeZone</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>instante de tiempo.</t>
+          <t>huso horario</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>An ontology for time zone descriptions was described in [owl-time-20060927] and provided as RDF in a separate namespace tzont:. However, that ontology was incomplete in scope, and the example datasets were selective. Furthermore, since the use of a class from an external ontology as the range of an ObjectProperty in OWL-Time creates a dependency, reference to the time zone class has been replaced with the 'stub' class in the normative part of this version of OWL-Time.</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>A temporal entity with zero extent or duration</t>
+          <t>Una entidad temporal con una extensión o duración cero.</t>
         </is>
       </c>
     </row>
@@ -5422,75 +5422,75 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>Time instant</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>intervalo de fecha-hora</t>
+          <t>instante de tiempo.</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>instante de tiempo.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>intervalo de fecha-hora</t>
+          <t>instante de tiempo.</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Date-time interval</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>intervalo de fecha-hora</t>
+          <t>instante de tiempo.</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>A temporal entity with zero extent or duration</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>intervalo de fecha-hora</t>
+          <t>instante de tiempo.</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>:DateTimeInterval can only be used for an interval whose limits coincide with a date-time element aligned to the calendar and timezone indicated. For example, while both have a duration of one day, the 24-hour interval beginning at midnight at the beginning of 8 May in Central Europe can be expressed as a :DateTimeInterval, but the 24-hour interval starting at 1:30pm cannot.</t>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>intervalo de fecha-hora</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>'intervalo de fecha-hora' es una subclase de 'intervalo propio', definida utilizando el multi-elemento 'descripción de fecha-hora'.</t>
+          <t>Date-time interval</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>'intervalo de fecha-hora' se puede utilizar sólo para un intervalo cuyos límites coinciden con un elemento de fecha-hora alineados con el calendario y la zona horaria indicados. Por ejemplo, aunque ambos tienen una duración de un día, el intervalo de 24 horas que empieza en la media noche del comienzo del 8 mayo en Europa Central se puede expresar como un 'intervalo de fecha-hora', el intervalo de 24 horas que empieza a las 1:30pm no.</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
     </row>
@@ -5558,75 +5558,75 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>DateTimeInterval is a subclass of ProperInterval, defined using the multi-element DateTimeDescription.</t>
+          <t>:DateTimeInterval can only be used for an interval whose limits coincide with a date-time element aligned to the calendar and timezone indicated. For example, while both have a duration of one day, the 24-hour interval beginning at midnight at the beginning of 8 May in Central Europe can be expressed as a :DateTimeInterval, but the 24-hour interval starting at 1:30pm cannot.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>intervalo de tiempo</t>
+          <t>intervalo de fecha-hora</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>intervalo de tiempo</t>
+          <t>intervalo de fecha-hora</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>intervalo de tiempo</t>
+          <t>intervalo de fecha-hora</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>A temporal entity with an extent or duration</t>
+          <t>'intervalo de fecha-hora' es una subclase de 'intervalo propio', definida utilizando el multi-elemento 'descripción de fecha-hora'.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>intervalo de tiempo</t>
+          <t>intervalo de fecha-hora</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>'intervalo de fecha-hora' se puede utilizar sólo para un intervalo cuyos límites coinciden con un elemento de fecha-hora alineados con el calendario y la zona horaria indicados. Por ejemplo, aunque ambos tienen una duración de un día, el intervalo de 24 horas que empieza en la media noche del comienzo del 8 mayo en Europa Central se puede expresar como un 'intervalo de fecha-hora', el intervalo de 24 horas que empieza a las 1:30pm no.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#DateTimeInterval</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>intervalo de tiempo</t>
+          <t>intervalo de fecha-hora</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalEntity</t>
+          <t>DateTimeInterval is a subclass of ProperInterval, defined using the multi-element DateTimeDescription.</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Una entidad temporal con una extensión o duración.</t>
+          <t>intervalo de tiempo</t>
         </is>
       </c>
     </row>
@@ -5660,75 +5660,75 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Time interval</t>
+          <t>A temporal entity with an extent or duration</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>intervalo de tiempo</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Instant</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>intervalo de tiempo</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Una entidad temporal con extensión o duración distinta de cero, es decir, para la cual los valores de principio y fin del intervalo son diferentes.</t>
+          <t>http://www.w3.org/2006/time#TemporalEntity</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>intervalo de tiempo</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Una entidad temporal con una extensión o duración.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#ProperInterval</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>intervalo de tiempo</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Proper interval</t>
+          <t>Time interval</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#Interval</t>
+          <t>http://www.w3.org/2006/time#Instant</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>intervalo propio</t>
+          <t>Una entidad temporal con extensión o duración distinta de cero, es decir, para la cual los valores de principio y fin del intervalo son diferentes.</t>
         </is>
       </c>
     </row>
@@ -5779,75 +5779,75 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>A temporal entity with non-zero extent or duration, i.e., for which the value of the beginning and end are different</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>intervalo propio</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feature at risk - added in 2017 revision, and not yet widely used. </t>
+          <t>Proper interval</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>intervalo propio</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Membership of the class :MonthOfYear is open, to allow for alternative annual calendars and different month names.</t>
+          <t>http://www.w3.org/2006/time#Interval</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>intervalo propio</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b42</t>
+          <t>intervalo propio</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#MonthOfYear</t>
+          <t>http://www.w3.org/2006/time#ProperInterval</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>intervalo propio</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b37</t>
+          <t>A temporal entity with non-zero extent or duration, i.e., for which the value of the beginning and end are different</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b39</t>
+          <t xml:space="preserve">Feature at risk - added in 2017 revision, and not yet widely used. </t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Month of year</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b40</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b40</t>
+          <t>Membership of the class :MonthOfYear is open, to allow for alternative annual calendars and different month names.</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b42</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b44</t>
+          <t>Month of year</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b43</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b39</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>mes del año</t>
+          <t>http://www.w3.org/2006/time#DateTimeDescription</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>The month of the year</t>
+          <t>mes del año</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La pertenencia a la clase 'mes del año' está abierta, a permitir calendarios anuales alternativos y diferentes nombres de meses.</t>
+          <t>The month of the year</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>El mes del año.</t>
+          <t>La pertenencia a la clase 'mes del año' está abierta, a permitir calendarios anuales alternativos y diferentes nombres de meses.</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Característica en riesgo - añadida en la revisión de 2017, y no utilizada todavía de forma amplia.</t>
+          <t>El mes del año.</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b38</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b37</t>
         </is>
       </c>
     </row>
@@ -6085,75 +6085,75 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b41</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b44</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t>mes del año</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Una posición temporal descrita utilizando bien un valor (nominal) de un sistema de referencia ordinal, o un valor (numérico) en un sistema de coordenadas temporales.</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b41</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t>mes del año</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Time position</t>
+          <t>Característica en riesgo - añadida en la revisión de 2017, y no utilizada todavía de forma amplia.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t>mes del año</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b48</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b43</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TimePosition</t>
+          <t>http://www.w3.org/2006/time#MonthOfYear</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t>mes del año</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t xml:space="preserve">A temporal position described using either a (nominal) value from an ordinal reference system, or a (numeric) value in a temporal coordinate system. </t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b38</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Una posición temporal descrita utilizando bien un valor (nominal) de un sistema de referencia ordinal, o un valor (numérico) en un sistema de coordenadas temporales.</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>Time position</t>
         </is>
       </c>
     </row>
@@ -6204,92 +6204,92 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>posición de tiempo</t>
+          <t xml:space="preserve">A temporal position described using either a (nominal) value from an ordinal reference system, or a (numeric) value in a temporal coordinate system. </t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>posición temporal</t>
+          <t>posición de tiempo</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>CCOT-Time structural matching spreadsheet identified cco:ont00000359 (Julian Date) as overlapping with this class. No further axioms are added here because that would push constraints from the narrower CCOT class onto this broader Time class.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>posición temporal</t>
+          <t>posición de tiempo</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Una posición sobre una línea de tiempo.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>posición de tiempo</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
           <t>http://www.w3.org/2006/time#TemporalPosition</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>posición temporal</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>posición temporal</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>posición temporal</t>
+          <t>posición de tiempo</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>n8af765655db349cd8d357fb5dec18556b47</t>
+          <t>n1966d7df8142454f9c21ad217dfdb174b48</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>posición temporal</t>
+          <t>posición de tiempo</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>A position on a time-line</t>
+          <t>posición de tiempo</t>
         </is>
       </c>
     </row>
@@ -6306,228 +6306,330 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Temporal position</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Una posición sobre una línea de tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>CCOT-Time structural matching spreadsheet identified cco:ont00000223 (Time of Day) as overlapping with this class. No further axioms are added here because that would push constraints from the narrower CCOT class onto this broader Time class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>A position on a time-line</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>n1966d7df8142454f9c21ad217dfdb174b47</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>posición temporal</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Temporal position</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B350" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C350" t="inlineStr">
         <is>
           <t>Un sistema de referencia temporal, tal como un sistema de coordenadas temporales (con un origen, una dirección y una escala), una combinación calendario-reloj, o un sistema ordinal (posiblemente jerárquico).
     Esta clase comodín representa el conjunto de todos los sistemas de referencia temporal.</t>
         </is>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
+    <row r="351">
+      <c r="A351" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C351" t="inlineStr">
         <is>
           <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
+    <row r="352">
+      <c r="A352" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
+      <c r="C352" t="inlineStr">
         <is>
           <t>Temporal Reference System</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
+    <row r="353">
+      <c r="A353" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="C353" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
+    <row r="354">
+      <c r="A354" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
+      <c r="C354" t="inlineStr">
         <is>
           <t>En el ISO 19108:2002 [ISO19108] se proporciona una taxonomía de sistemas de referencia temporal, incluyendo (a) sistemas de calendario + reloj; (b) sistemas de coordenadas temporales (es decir, desplazamiento numérico a partir de una época); (c) sistemas de referencia ordinales temporales (es decir, secuencia ordenada de intervalos nombrados, no necesariamente de igual duración).</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
+      <c r="C355" t="inlineStr">
         <is>
           <t>A taxonomy of temporal reference systems is provided in ISO 19108:2002 [ISO19108], including (a) calendar + clock systems; (b) temporal coordinate systems (i.e., numeric offset from an epoch); (c) temporal ordinal reference systems (i.e., ordered sequence of named intervals, not necessarily of equal duration).</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
+    <row r="356">
+      <c r="A356" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TRS</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>sistema de referencia temporal</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
+      <c r="C356" t="inlineStr">
         <is>
           <t>A temporal reference system, such as a temporal coordinate system (with an origin, direction, and scale), a calendar-clock combination, or a (possibly hierarchical) ordinal system. 
 This is a stub class, representing the set of all temporal reference systems.</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B357" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
+      <c r="C357" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C358" t="inlineStr">
         <is>
           <t>A standard duration, which provides a scale factor for a time extent, or the granularity or precision for a time position.</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C359" t="inlineStr">
         <is>
           <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+    <row r="360">
+      <c r="A360" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C360" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalDuration</t>
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
+    <row r="361">
+      <c r="A361" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C361" t="inlineStr">
         <is>
           <t>Una duración estándar, que proporciona un factor de escala para una extensión de tiempo, o la granularidad o precisión para una posición de tiempo.</t>
         </is>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C362" t="inlineStr">
         <is>
           <t>Remove enumeration from definition, in order to allow other units to be used when required in other coordinate systems. 
 NOTE: existing units are still present as members of the class, but the class membership is now open. 
@@ -6544,52 +6646,52 @@
         </is>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
+    <row r="363">
+      <c r="A363" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C363" t="inlineStr">
         <is>
           <t>La pertenencia de la clase 'unidad de tiempo' está abierta, para permitir otras unidades de tiempo utilizadas en algunas aplicaciones técnicas (por ejemplo, millones de años o el mes Baha'i).</t>
         </is>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
+    <row r="364">
+      <c r="A364" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C364" t="inlineStr">
         <is>
           <t>Temporal unit</t>
         </is>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
+    <row r="365">
+      <c r="A365" t="inlineStr">
         <is>
           <t>http://www.w3.org/2006/time#TemporalUnit</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B365" t="inlineStr">
         <is>
           <t>unidad de tiempo</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C365" t="inlineStr">
         <is>
           <t>Membership of the class TemporalUnit is open, to allow for other temporal units used in some technical applications (e.g., millions of years, Baha'i month).</t>
         </is>
